--- a/综招查证清单.xlsx
+++ b/综招查证清单.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="综招总表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待查证事项" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待核实事项" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'综招总表'!$A$1:$P$20</definedName>
@@ -450,15 +450,15 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="46" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -499,37 +499,37 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>校测环节</t>
+          <t>校测形式</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>校测形式</t>
+          <t>校测地点</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>校测地点</t>
+          <t>入围比例</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>入围比例</t>
+          <t>综合成绩折算</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>综合成绩折算</t>
+          <t>高考成绩要求</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>高考成绩要求</t>
+          <t>招生条目数</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>招生专业(类)数</t>
+          <t>具体专业数</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -539,11 +539,11 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>备注/待核</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="46" customHeight="1">
+          <t>待核实</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -582,31 +582,29 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>综合面试，满分100分；专家、考场、考生“三随机”抽签，全程录音录像</t>
+          <t>山东大学中心校区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>山东大学中心校区</t>
+          <t>1:6（分组别）</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>1:6（分组别）</t>
+          <t>高考85% + 校测15%</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>高考85% + 校测15%</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
           <t>高考总成绩不低于山东省2026年特殊类型招生控制线</t>
         </is>
       </c>
+      <c r="M2" s="2" t="n">
+        <v>23</v>
+      </c>
       <c r="N2" s="2" t="n">
-        <v>23</v>
+        <v>209</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -615,7 +613,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="46" customHeight="1">
+    <row r="3" ht="44" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -644,7 +642,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待查证</t>
+          <t>6月19日·面试</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -654,28 +652,26 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>考核方式为面试，重点考察关键能力、学科素养与思维品质；简章写明“高考结束后、成绩公布前”进行，具体安排另行公布</t>
+          <t>中国海洋大学崂山校区（青岛市崂山区松岭路238号）</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待查证</t>
+          <t>1:6（分专业）</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>1:6（分专业）</t>
+          <t>高考85% + 校测15%</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>高考85% + 校测15%</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
           <t>高考投档成绩不低于山东省2026年特殊类型招生控制线</t>
         </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>4</v>
@@ -685,13 +681,9 @@
           <t>http://bkzs.ouc.edu.cn/2024/0422/c17839a524977/page.htm</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>校测日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="46" customHeight="1">
+      <c r="P3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4" ht="44" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -730,44 +722,38 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>学校考核为面试；综合成绩=高考投档成绩×85%+学校考核成绩×15%</t>
+          <t>待查证</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待查证</t>
+          <t>1:6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1:6</t>
+          <t>高考85% + 校测15%</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>高考85% + 校测15%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
           <t>高考总成绩对应位次须位于山东省前50000名</t>
         </is>
       </c>
+      <c r="M4" s="2" t="n">
+        <v>26</v>
+      </c>
       <c r="N4" s="2" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://zhaosheng.upc.edu.cn/cms/frontViewArticle.html?id=5b66a8ff3f0e4f04a74e1f74ca521c10</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>分专业计划</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
+      <c r="P4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -806,44 +792,38 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>面试满分100分，重点考查逻辑思维、人文素养、表达能力及创新意识；6月18日现场报到</t>
+          <t>哈尔滨工业大学（威海）</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>哈尔滨工业大学（威海）</t>
+          <t>1:6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1:6</t>
+          <t>高考85% + 面试15%</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>高考85% + 面试15%</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
           <t>入围考生高考总成绩不低于山东省2026年特殊类型招生控制线</t>
         </is>
       </c>
+      <c r="M5" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="N5" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>http://zsb.hitwh.edu.cn/home/article/details?id=1576</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>分专业计划</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
+      <c r="P5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="44" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -882,28 +862,26 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>笔试6月14日（线上），按不超过招生计划10倍划定合格线；面试6月16日（线上）</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>面试1:10（笔试合格线）</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>面试1:10（笔试合格线）</t>
+          <t>高考70% + 面试30%</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>高考70% + 面试30%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
           <t>面试入围考生高考成绩须达到山东省2026年特殊类型招生控制线</t>
         </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>7</v>
@@ -915,7 +893,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr"/>
     </row>
-    <row r="7" ht="46" customHeight="1">
+    <row r="7" ht="44" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -954,31 +932,29 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>笔试6月14日上午，按不低于各专业组招生计划10倍划定合格线；面试6月16日</t>
+          <t>笔试线上；面试：山东师范大学</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>笔试线上；面试：山东师范大学</t>
+          <t>面试1:10（笔试合格线）</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>面试1:10（笔试合格线）</t>
+          <t>高考70% + 面试30%</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>高考70% + 面试30%</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
           <t>分组要求：组1、组2达特招线；组3达一段线且不低于特招线下10分；组4、组5达一段线且不低于特招线下20分</t>
         </is>
       </c>
+      <c r="M7" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="N7" s="2" t="n">
-        <v>19</v>
+        <v>126</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -987,7 +963,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr"/>
     </row>
-    <row r="8" ht="46" customHeight="1">
+    <row r="8" ht="44" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -1026,28 +1002,26 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>笔试6月14日上午；面试6月16日上午；考核方式“综合素质笔试+综合素质面试”</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>按笔试成绩划定面试资格</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>按笔试成绩划定面试资格</t>
+          <t>高考70% + 面试30%</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>高考70% + 面试30%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
           <t>高考成绩不低于山东省2026年特殊类型招生控制线下20分（以简章为准）</t>
         </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>11</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>11</v>
@@ -1059,7 +1033,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr"/>
     </row>
-    <row r="9" ht="46" customHeight="1">
+    <row r="9" ht="44" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -1098,28 +1072,26 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>笔试6月14日（线上，综合素质测试50%+专业素质测试50%，满分100）；面试6月17日（线上，满分100，60分合格</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>面试1:18（按组别）；入围1:6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>面试1:18（按组别）；入围1:6</t>
+          <t>高考70% + 面试30%</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>高考70% + 面试30%</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
           <t>高考成绩须达到山东省2026年普通高校特殊类型招生控制线</t>
         </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>19</v>
@@ -1131,7 +1103,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr"/>
     </row>
-    <row r="10" ht="46" customHeight="1">
+    <row r="10" ht="44" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -1170,31 +1142,29 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>线上笔试6月14日（两科：财经基本素养、财经应用能力，均为选择题，满分100），按1:10确定面试名单；线上面试6月16</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>面试1:10；入围1:6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>面试1:10；入围1:6</t>
+          <t>高考×70% + 面试×7.5×30%</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>高考×70% + 面试×7.5×30%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
           <t>高考成绩须达到山东省2026年特殊类型招生控制线</t>
         </is>
       </c>
+      <c r="M10" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="N10" s="2" t="n">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1203,7 +1173,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr"/>
     </row>
-    <row r="11" ht="46" customHeight="1">
+    <row r="11" ht="44" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -1242,28 +1212,26 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>机试6月13日9:00—11:30（济南等6考点，满分150，数学/英语/物理/化学选择题）；山东等4省市面试6月15日</t>
+          <t>机试济南考点；面试线上</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>机试济南考点；面试线上</t>
+          <t>机试成绩公布后划定面试名单</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>机试成绩公布后划定面试名单</t>
+          <t>高考60% + 校测30% + 学业水平10%（631）</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>高考60% + 校测30% + 学业水平10%（631）</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
           <t>高考投档成绩须达到山东省普通类特殊类型招生控制线</t>
         </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>9</v>
@@ -1273,13 +1241,9 @@
           <t>https://admission.scut.edu.cn/2026/0416/c30825a624737/page.htm</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t>分专业计划</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1">
+      <c r="P11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="44" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -1318,28 +1282,26 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>专家面试约60分钟/组（约5名考生、3位专家），考察数理基础、逻辑推理、学习兴趣与表达；面试后统一进行体育测试（立定跳远</t>
+          <t>青岛·国科大海洋学院（黄岛区海军路88号乙）</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>青岛·国科大海洋学院（黄岛区海军路88号乙）</t>
+          <t>按综合评价成绩择优（提前批）</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>按综合评价成绩择优（提前批）</t>
+          <t>高考60% + 校测30% + 学业水平10%</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>高考60% + 校测30% + 学业水平10%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
           <t>简章未单列分数门槛；高考成绩公布后按合成成绩在提前批择优</t>
         </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>14</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>14</v>
@@ -1351,7 +1313,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr"/>
     </row>
-    <row r="13" ht="46" customHeight="1">
+    <row r="13" ht="44" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -1390,28 +1352,26 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6月13日：文理基础14:00—15:45、口试16:45—17:15、写作17:15—18:35；另报丘成桐班者6月1</t>
+          <t>济南、青岛等考点（可填两个意向城市）</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>济南、青岛等考点（可填两个意向城市）</t>
+          <t>不超过招生计划5倍入围</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>不超过招生计划5倍入围</t>
+          <t>高考60% + 入学测试30% + 学业水平10%</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>高考60% + 入学测试30% + 学业水平10%</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
           <t>高考总成绩须达山东省特殊类型招生控制线；11门学业水平合格考均须合格</t>
         </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>26</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>26</v>
@@ -1421,13 +1381,9 @@
           <t>https://admissions.cuhk.edu.cn/article/2379</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>分专业计划</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1">
+      <c r="P13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="44" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -1468,31 +1424,29 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>校园日活动共6场、横跨3个周末（3/14—3/29）：团队活动、英文写作、模拟课堂、校园参观；初审结果3月公布，A/B档</t>
+          <t>上海纽约大学（上海）</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>上海纽约大学（上海）</t>
+          <t>材料初审→校园日→A/B档</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>材料初审→校园日→A/B档</t>
+          <t>无固定比例：初审+校园日+高考，结论分A档（预录取）/B档（待录取）</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>无固定比例：初审+校园日+高考，结论分A档（预录取）/B档（待录取）</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
           <t>A档：高考达山东省特招线即录取；B档：达线后再综合评定择优；须在提前批/综合评价批次第一志愿填报</t>
         </is>
       </c>
+      <c r="M14" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="N14" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1501,11 +1455,11 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>山东计划数；分专业计划</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="46" customHeight="1">
+          <t>山东计划数</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -1546,28 +1500,26 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>①线上AI面试（各自轮次截止后指定窗口完成，考察英文表达与思维）②线下校园日一天：面试、英文写作笔试、模拟课堂、校园参观</t>
+          <t>昆山杜克大学（江苏昆山）</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>昆山杜克大学（江苏昆山）</t>
+          <t>综合评估后入围，5月公示</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>综合评估后入围，5月公示</t>
+          <t>6-4：高考60% + 学校自主综合评估40%</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6-4：高考60% + 学校自主综合评估40%</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
           <t>入围后高考成绩须达山东省特招线；提前批第一志愿填报，未录取不影响后续批次</t>
         </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>14</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>14</v>
@@ -1579,11 +1531,11 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>山东计划数；分专业计划</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1">
+          <t>山东计划数</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -1622,28 +1574,26 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>机试6月13日9:15—11:15（8:15入场、9:00—9:15样题练习，闭卷：数学40+物理40+英语20，120</t>
+          <t>机试：济南、青岛；面试：分省线下（山东日期以招生组通知为准）</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>机试：济南、青岛；面试：分省线下（山东日期以招生组通知为准）</t>
+          <t>机试成绩划线进入面试</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>机试成绩划线进入面试</t>
+          <t>高考60% + 能力测试30%（机试25%+面试5%）+ 平时成绩10%</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>高考60% + 能力测试30%（机试25%+面试5%）+ 平时成绩10%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
           <t>高考成绩不低于山东省特殊类型招生控制线</t>
         </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>3</v>
@@ -1655,7 +1605,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr"/>
     </row>
-    <row r="17" ht="46" customHeight="1">
+    <row r="17" ht="44" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -1694,28 +1644,26 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6月12日：8:30—9:40 外语（英语/俄语，机试）；10:40—12:40 数学（机试+笔试结合）或文学（机试）</t>
+          <t>济南、青岛</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>济南、青岛</t>
+          <t>按学校测试成绩划定</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>按学校测试成绩划定</t>
+          <t>高考60% + 学校测试30% + 学业水平10%</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>高考60% + 学校测试30% + 学业水平10%</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
           <t>高考成绩不低于山东省特殊类型招生控制线；学考各科合格且达C级及以上</t>
         </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>16</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>16</v>
@@ -1727,7 +1675,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr"/>
     </row>
-    <row r="18" ht="46" customHeight="1">
+    <row r="18" ht="44" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -1766,28 +1714,26 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6月14日9:00—12:00、14:00—16:00报到，6月14日校园开放日；6月15日能力测试：外语口试25分+中</t>
+          <t>北京外国语大学西校区国际大厦</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>北京外国语大学西校区国际大厦</t>
+          <t>按能力测试成绩划线</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>按能力测试成绩划线</t>
+          <t>高考实考分70% + 能力测试30%</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>高考实考分70% + 能力测试30%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
           <t>高考实考分不低于山东省普通类特殊类型招生控制线</t>
         </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>35</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>35</v>
@@ -1797,13 +1743,9 @@
           <t>https://joinus.bfsu.edu.cn/info/1072/11494.htm</t>
         </is>
       </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t>分专业计划</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="46" customHeight="1">
+      <c r="P18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="44" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -1842,28 +1784,26 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6月10日—20日分多期分场次举行，每位考生指定一场（高考后），多位教授面试约15分钟/人</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>开放日成绩分A/B/C档</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>开放日成绩分A/B/C档</t>
+          <t>高考成绩 + 校园开放日成绩（A档+20、B档+15、C档+10）相加排序</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>高考成绩 + 校园开放日成绩（A档+20、B档+15、C档+10）相加排序</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
           <t>高考成绩不低于山东省特殊类型招生控制线</t>
         </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>11</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>11</v>
@@ -1875,7 +1815,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr"/>
     </row>
-    <row r="20" ht="46" customHeight="1">
+    <row r="20" ht="44" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -1914,28 +1854,26 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6月12日—14日综合测试（多样化考查方式，含面试）并含体育测试（所有考生必考）；准考证6月3日起打印</t>
+          <t>杭州·西湖大学云谷校区</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>杭州·西湖大学云谷校区</t>
+          <t>按综合测试成绩划线</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>按综合测试成绩划线</t>
+          <t>高考60% + 学校综合测试30% + 学业水平10%</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>高考60% + 学校综合测试30% + 学业水平10%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
           <t>高考总分（含政策加分）不低于山东省普通类特殊类型招生控制线，提前批A类填报</t>
         </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>1</v>
@@ -1959,13 +1897,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1990,18 +1928,18 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
+    <row r="2">
       <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>中国海洋大学</t>
+          <t>上海纽约大学</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>校测日期</t>
+          <t>山东计划数</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2010,141 +1948,21 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
+    <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>中国石油大学（华东）</t>
+          <t>昆山杜克大学</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>分专业计划</t>
+          <t>山东计划数</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>学校本科招生网 / 山东省教育招生考试院《填报志愿指南》</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>哈尔滨工业大学（威海）</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>分专业计划</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>学校本科招生网 / 山东省教育招生考试院《填报志愿指南》</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>华南理工大学</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>分专业计划</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>学校本科招生网 / 山东省教育招生考试院《填报志愿指南》</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>香港中文大学（深圳）</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>分专业计划</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>学校本科招生网 / 山东省教育招生考试院《填报志愿指南》</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>上海纽约大学</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>山东计划数；分专业计划</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>学校本科招生网 / 山东省教育招生考试院《填报志愿指南》</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>昆山杜克大学</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>山东计划数；分专业计划</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>学校本科招生网 / 山东省教育招生考试院《填报志愿指南》</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>北京外国语大学</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>分专业计划</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
         <is>
           <t>学校本科招生网 / 山东省教育招生考试院《填报志愿指南》</t>
         </is>
